--- a/outputs/39190.xlsx
+++ b/outputs/39190.xlsx
@@ -117,16 +117,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -383,454 +387,454 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A2,$F$2:$F$8,0)),"Delete","")</f>
-        <v>Delete</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="C2" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A2)&gt;0,"Delete","")</f>
+        <v>Delete</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>108</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A3,$F$2:$F$8,0)),"Delete","")</f>
-        <v>Delete</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="C3" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A3)&gt;0,"Delete","")</f>
+        <v>Delete</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A4,$F$2:$F$8,0)),"Delete","")</f>
-        <v>Delete</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="C4" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A4)&gt;0,"Delete","")</f>
+        <v>Delete</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>140</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A5,$F$2:$F$8,0)),"Delete","")</f>
-        <v>Delete</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="C5" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A5)&gt;0,"Delete","")</f>
+        <v>Delete</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>160</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A6,$F$2:$F$8,0)),"Delete","")</f>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="n">
+      <c r="C6" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A6)&gt;0,"Delete","")</f>
+        <v/>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A7,$F$2:$F$8,0)),"Delete","")</f>
-        <v/>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="C7" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A7)&gt;0,"Delete","")</f>
+        <v/>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A8,$F$2:$F$8,0)),"Delete","")</f>
-        <v/>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="C8" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A8)&gt;0,"Delete","")</f>
+        <v/>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A9,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C9" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A9)&gt;0,"Delete","")</f>
         <v>Delete</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A10,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C10" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A10)&gt;0,"Delete","")</f>
         <v>Delete</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A11,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C11" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A11)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A12,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C12" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A12)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A13,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C13" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A13)&gt;0,"Delete","")</f>
         <v>Delete</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A14,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C14" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A14)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C15" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A15,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C15" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A15)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C16" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A16,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C16" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A16)&gt;0,"Delete","")</f>
         <v>Delete</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C17" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A17,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C17" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A17)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A18,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C18" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A18)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A19,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C19" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A19)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A20,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C20" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A20)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A21,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C21" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A21)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A22,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C22" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A22)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A23,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C23" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A23)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C24" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A24,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C24" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A24)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A25,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C25" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A25)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A26,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C26" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A26)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C27" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A27,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C27" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A27)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A28,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C28" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A28)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C29" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A29,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C29" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A29)&gt;0,"Delete","")</f>
         <v>Delete</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C30" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A30,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C30" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A30)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A31,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C31" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A31)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A32,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C32" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A32)&gt;0,"Delete","")</f>
         <v>Delete</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C33" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A33,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C33" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A33)&gt;0,"Delete","")</f>
         <v>Delete</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C34" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A34,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C34" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A34)&gt;0,"Delete","")</f>
         <v>Delete</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C35" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A35,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C35" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A35)&gt;0,"Delete","")</f>
         <v>Delete</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C36" s="2" t="str">
-        <f aca="false">IF(ISNUMBER(MATCH(A36,$F$2:$F$8,0)),"Delete","")</f>
+      <c r="C36" s="3" t="str">
+        <f aca="false">IF(COUNTIF($F$2:$F$8,A36)&gt;0,"Delete","")</f>
         <v/>
       </c>
     </row>

--- a/outputs/39190.xlsx
+++ b/outputs/39190.xlsx
@@ -117,7 +117,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -126,11 +126,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -386,7 +390,7 @@
   <dimension ref="A1:F36"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -397,444 +401,444 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A2)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="C2" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A2,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A3)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="C3" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A3,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A4)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="C4" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A4,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A5)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-      <c r="F5" s="2" t="n">
+      <c r="C5" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A5,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>160</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A6)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-      <c r="F6" s="2" t="n">
+      <c r="C6" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A6,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>102</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A7)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-      <c r="F7" s="2" t="n">
+      <c r="C7" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A7,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>101</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A8)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-      <c r="F8" s="2" t="n">
+      <c r="C8" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A8,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>105</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A9)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A9,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A10)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="C10" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A10,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A11)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="C11" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A11,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A12)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A12,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A13)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="C13" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A13,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A14)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+      <c r="C14" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A14,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C15" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A15)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A15,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C16" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A16)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+      <c r="C16" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A16,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C17" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A17)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+      <c r="C17" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A17,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A18)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+      <c r="C18" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A18,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A19)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+      <c r="C19" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A19,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A20)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+      <c r="C20" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A20,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A21)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+      <c r="C21" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A21,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A22)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+      <c r="C22" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A22,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A23)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
+      <c r="C23" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A23,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C24" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A24)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+      <c r="C24" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A24,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A25)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
+      <c r="C25" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A25,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C26" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A26)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+      <c r="C26" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A26,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C27" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A27)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+      <c r="C27" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A27,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A28)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A28,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C29" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A29)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
+      <c r="C29" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A29,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C30" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A30)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
+      <c r="C30" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A30,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A31)&gt;0,"Delete","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A31,F:F,0)),"Delete","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A32)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A32,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C33" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A33)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C33" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A33,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="n">
         <v>160</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C34" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A34)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C34" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A34,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C35" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A35)&gt;0,"Delete","")</f>
-        <v>Delete</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
+      <c r="C35" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A35,F:F,0)),"Delete","")</f>
+        <v>Delete</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C36" s="3" t="str">
-        <f aca="false">IF(COUNTIF($F$2:$F$8,A36)&gt;0,"Delete","")</f>
+      <c r="C36" s="1" t="str">
+        <f aca="false">IF(ISNUMBER(MATCH(A36,F:F,0)),"Delete","")</f>
         <v/>
       </c>
     </row>
